--- a/Result/profitability/1516.xlsx
+++ b/Result/profitability/1516.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8825</v>
+        <v>-0.845</v>
       </c>
       <c r="N2" t="n">
-        <v>5.49625</v>
+        <v>5.523750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>-0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.89625</v>
+        <v>-0.0975</v>
       </c>
       <c r="N3" t="n">
-        <v>4.77625</v>
+        <v>4.8975</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-4.16</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6075</v>
+        <v>-0.61375</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2825</v>
+        <v>5.29625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.62625</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1.14625</v>
+        <v>1.16625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6300000000000001</v>
+        <v>-0.6637500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>1.10875</v>
+        <v>0.7625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.2</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6787500000000001</v>
+        <v>-0.6825000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1987500000000003</v>
+        <v>0.1999999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6875</v>
+        <v>-0.6912499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.3525000000000002</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.7250000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7362499999999997</v>
+        <v>-0.7362500000000002</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.69125</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7599999999999998</v>
+        <v>-0.7600000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9810,6 +9810,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>29</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-12.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.8674999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7400000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1211129296235679</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.009999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03071017274472165</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
